--- a/data/trans_dic/P15D$urgencias-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,85; 70,96</t>
+          <t>36,11; 72,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,48; 75,42</t>
+          <t>51,31; 76,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,69; 82,42</t>
+          <t>55,4; 82,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,42; 100,0</t>
+          <t>42,45; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 74,1</t>
+          <t>16,57; 72,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,88; 70,56</t>
+          <t>37,66; 72,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,28; 94,87</t>
+          <t>56,74; 94,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,93; 82,39</t>
+          <t>16,3; 84,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,61; 67,66</t>
+          <t>36,48; 66,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,08; 70,2</t>
+          <t>50,52; 70,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,88; 84,97</t>
+          <t>61,39; 84,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,55; 86,59</t>
+          <t>41,89; 88,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,91; 63,88</t>
+          <t>29,75; 65,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,96; 74,17</t>
+          <t>52,34; 73,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,22; 77,2</t>
+          <t>51,13; 76,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,78; 79,57</t>
+          <t>26,89; 80,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,39; 94,74</t>
+          <t>54,92; 94,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,1; 71,19</t>
+          <t>38,53; 71,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,04; 79,56</t>
+          <t>37,22; 79,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 71,51</t>
+          <t>21,51; 72,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,02; 71,24</t>
+          <t>42,68; 69,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,22; 69,47</t>
+          <t>49,8; 69,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53,23; 74,57</t>
+          <t>52,72; 74,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 70,76</t>
+          <t>31,84; 68,74</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,65; 62,81</t>
+          <t>12,14; 62,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,23; 67,03</t>
+          <t>39,08; 68,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46,07; 79,24</t>
+          <t>45,8; 79,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,07; 88,83</t>
+          <t>57,27; 89,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,04; 84,6</t>
+          <t>28,05; 84,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,2; 72,71</t>
+          <t>39,1; 74,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,07; 75,43</t>
+          <t>34,57; 76,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,21; 76,31</t>
+          <t>46,21; 77,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,11; 64,14</t>
+          <t>27,16; 64,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,43; 65,95</t>
+          <t>43,39; 65,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,66; 73,34</t>
+          <t>46,76; 72,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,3; 80,8</t>
+          <t>58,17; 79,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,45; 60,72</t>
+          <t>14,3; 60,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,75; 65,23</t>
+          <t>31,41; 65,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,0; 77,86</t>
+          <t>40,46; 77,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,97; 72,77</t>
+          <t>43,34; 72,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,17; 90,79</t>
+          <t>22,95; 89,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,28; 78,34</t>
+          <t>42,85; 77,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,17; 91,33</t>
+          <t>51,24; 91,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,77; 66,95</t>
+          <t>38,76; 67,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,76; 64,29</t>
+          <t>24,42; 63,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41,69; 65,45</t>
+          <t>42,15; 66,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,29; 79,16</t>
+          <t>53,57; 78,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,79; 67,01</t>
+          <t>46,71; 67,49</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,27</t>
+          <t>0,0; 69,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,06; 91,46</t>
+          <t>34,37; 92,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,28; 84,83</t>
+          <t>30,46; 84,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,45; 68,39</t>
+          <t>31,68; 67,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,75; 90,87</t>
+          <t>33,26; 90,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,82; 80,21</t>
+          <t>48,96; 79,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,4; 84,64</t>
+          <t>51,02; 84,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,08; 75,95</t>
+          <t>50,16; 74,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,0; 73,25</t>
+          <t>28,5; 72,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52,27; 78,29</t>
+          <t>51,69; 77,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,8; 78,6</t>
+          <t>49,65; 78,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,98; 66,78</t>
+          <t>47,19; 67,88</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,92; 100,0</t>
+          <t>17,39; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,59; 66,72</t>
+          <t>18,37; 66,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,43; 68,3</t>
+          <t>8,11; 64,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,56; 63,78</t>
+          <t>21,7; 61,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,69; 81,81</t>
+          <t>20,64; 82,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,83; 56,96</t>
+          <t>19,09; 57,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,67; 69,61</t>
+          <t>31,79; 69,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,6; 60,26</t>
+          <t>37,19; 61,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34,13; 82,22</t>
+          <t>33,21; 81,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,38; 54,95</t>
+          <t>25,45; 54,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,81; 63,2</t>
+          <t>31,01; 60,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,0; 55,54</t>
+          <t>35,57; 56,7</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,24; 100,0</t>
+          <t>18,13; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,65; 81,27</t>
+          <t>38,96; 81,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,76; 57,01</t>
+          <t>10,95; 56,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,65; 52,13</t>
+          <t>19,7; 52,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,74; 85,03</t>
+          <t>48,21; 85,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,03; 65,47</t>
+          <t>37,28; 65,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,6; 82,06</t>
+          <t>46,19; 81,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,61; 47,36</t>
+          <t>28,1; 47,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46,64; 84,59</t>
+          <t>49,81; 84,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42,09; 64,96</t>
+          <t>43,38; 65,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41,21; 69,68</t>
+          <t>40,38; 70,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,83; 45,68</t>
+          <t>28,5; 45,14</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>36,34; 55,33</t>
+          <t>37,74; 55,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,06; 64,07</t>
+          <t>52,57; 64,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53,48; 67,38</t>
+          <t>53,96; 67,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,28; 66,3</t>
+          <t>50,95; 66,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,64; 74,35</t>
+          <t>54,77; 75,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,01; 62,1</t>
+          <t>49,35; 62,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,09; 71,8</t>
+          <t>57,57; 71,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,23; 56,89</t>
+          <t>44,81; 56,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47,39; 60,8</t>
+          <t>46,8; 61,38</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52,43; 61,04</t>
+          <t>52,96; 61,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57,64; 67,45</t>
+          <t>58,11; 68,37</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,97; 59,18</t>
+          <t>50,05; 60,15</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12763; 23925</t>
+          <t>12175; 24310</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30103; 44971</t>
+          <t>30598; 45690</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23612; 36250</t>
+          <t>24363; 36476</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8118; 19137</t>
+          <t>8123; 19137</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1787; 7845</t>
+          <t>1754; 7723</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10695; 21634</t>
+          <t>11548; 22315</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11191; 17326</t>
+          <t>10363; 17323</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3374; 16419</t>
+          <t>3248; 16817</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16660; 29976</t>
+          <t>16161; 29396</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46124; 63387</t>
+          <t>45613; 63358</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38516; 52890</t>
+          <t>38211; 52754</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15449; 33827</t>
+          <t>16365; 34741</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10100; 22317</t>
+          <t>10394; 22887</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43598; 61059</t>
+          <t>43084; 60824</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26051; 39263</t>
+          <t>26006; 39139</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7028; 21696</t>
+          <t>7332; 21868</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10090; 17578</t>
+          <t>10190; 17570</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14489; 27072</t>
+          <t>14652; 27133</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8855; 18043</t>
+          <t>8440; 18007</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3129; 10708</t>
+          <t>3221; 10810</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23013; 38105</t>
+          <t>22830; 37417</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61639; 83604</t>
+          <t>59931; 83654</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39141; 54833</t>
+          <t>38766; 54858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14125; 29888</t>
+          <t>13449; 29035</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1889; 9379</t>
+          <t>1812; 9296</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20417; 35799</t>
+          <t>20872; 36714</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16520; 28415</t>
+          <t>16424; 28359</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21859; 32868</t>
+          <t>21192; 33226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4299; 11349</t>
+          <t>3763; 11331</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10932; 21367</t>
+          <t>11490; 21903</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8535; 18894</t>
+          <t>8660; 19143</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12956; 21394</t>
+          <t>12954; 21586</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7402; 18182</t>
+          <t>7700; 18225</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36782; 54601</t>
+          <t>35926; 54423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28419; 44667</t>
+          <t>28477; 44118</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37919; 52550</t>
+          <t>37832; 51566</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2823; 11863</t>
+          <t>2794; 11855</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11483; 23587</t>
+          <t>11358; 23672</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11820; 22449</t>
+          <t>11664; 22473</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23305; 36894</t>
+          <t>21972; 36722</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2723; 8775</t>
+          <t>2218; 8676</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14442; 27409</t>
+          <t>14990; 27046</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13509; 22363</t>
+          <t>12546; 22310</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11687; 19674</t>
+          <t>11390; 19752</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7231; 18773</t>
+          <t>7132; 18421</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29664; 46567</t>
+          <t>29991; 47176</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27880; 42207</t>
+          <t>28560; 42099</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37472; 53661</t>
+          <t>37408; 54047</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6398</t>
+          <t>0; 6503</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4530; 11818</t>
+          <t>4441; 11895</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4236; 11866</t>
+          <t>4261; 11787</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9390; 19787</t>
+          <t>9167; 19563</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3726; 8970</t>
+          <t>3283; 8973</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20805; 33495</t>
+          <t>20443; 33066</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14997; 25694</t>
+          <t>15489; 25614</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18076; 26877</t>
+          <t>17750; 26380</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5388; 14095</t>
+          <t>5484; 14018</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28578; 42807</t>
+          <t>28265; 42319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22083; 34859</t>
+          <t>22018; 35017</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30217; 42955</t>
+          <t>30354; 43664</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>834; 4653</t>
+          <t>809; 4653</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3216; 11541</t>
+          <t>3178; 11501</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>922; 7466</t>
+          <t>887; 7033</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3837; 10386</t>
+          <t>3534; 9941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1886; 7456</t>
+          <t>1881; 7521</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4770; 14429</t>
+          <t>4835; 14492</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9865; 20397</t>
+          <t>9314; 20481</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11729; 19851</t>
+          <t>12250; 20266</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4699; 11319</t>
+          <t>4572; 11226</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10819; 23426</t>
+          <t>10847; 23270</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12799; 25428</t>
+          <t>12477; 24445</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17231; 27343</t>
+          <t>17513; 27914</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1438; 5933</t>
+          <t>1075; 5933</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9397; 17905</t>
+          <t>8583; 17932</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1634; 8657</t>
+          <t>1663; 8637</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4283; 10809</t>
+          <t>4086; 10797</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10110; 19217</t>
+          <t>10895; 19313</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20068; 35478</t>
+          <t>20203; 35443</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19504; 32932</t>
+          <t>18536; 32649</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15149; 25079</t>
+          <t>14877; 24953</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13308; 24137</t>
+          <t>14212; 24245</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32080; 49513</t>
+          <t>33065; 50266</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22795; 38544</t>
+          <t>22336; 38882</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21247; 33659</t>
+          <t>20998; 33262</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44731; 68097</t>
+          <t>46445; 68865</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>147737; 181822</t>
+          <t>149176; 181649</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>106766; 134514</t>
+          <t>107727; 135418</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>100593; 132643</t>
+          <t>101920; 132688</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>51253; 69745</t>
+          <t>51379; 70627</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>124644; 157938</t>
+          <t>125526; 158211</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>108617; 136617</t>
+          <t>109543; 136873</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>94485; 121523</t>
+          <t>95708; 120943</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>102779; 131867</t>
+          <t>101500; 133121</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>282136; 328442</t>
+          <t>284961; 331171</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>224745; 262987</t>
+          <t>226554; 266569</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>206704; 244820</t>
+          <t>207018; 248835</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$urgencias-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,11; 72,11</t>
+          <t>35,33; 71,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,31; 76,62</t>
+          <t>51,02; 75,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,4; 82,94</t>
+          <t>54,04; 82,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,45; 100,0</t>
+          <t>45,25; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,57; 72,95</t>
+          <t>17,06; 72,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,66; 72,78</t>
+          <t>38,1; 70,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,74; 94,85</t>
+          <t>61,83; 94,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,3; 84,39</t>
+          <t>20,74; 82,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,48; 66,35</t>
+          <t>37,81; 66,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,52; 70,17</t>
+          <t>50,67; 70,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,39; 84,75</t>
+          <t>62,25; 84,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,89; 88,93</t>
+          <t>43,37; 88,58</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 65,51</t>
+          <t>29,34; 63,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,34; 73,89</t>
+          <t>50,25; 73,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,13; 76,96</t>
+          <t>52,25; 78,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,89; 80,2</t>
+          <t>33,53; 79,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,92; 94,7</t>
+          <t>55,57; 94,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,53; 71,35</t>
+          <t>38,24; 71,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,22; 79,4</t>
+          <t>39,02; 81,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,51; 72,19</t>
+          <t>23,45; 72,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,68; 69,95</t>
+          <t>42,99; 70,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,8; 69,51</t>
+          <t>51,04; 69,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,72; 74,6</t>
+          <t>52,98; 74,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,84; 68,74</t>
+          <t>34,04; 71,61</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,14; 62,26</t>
+          <t>13,06; 62,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,08; 68,74</t>
+          <t>38,27; 67,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,8; 79,09</t>
+          <t>45,94; 79,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,27; 89,79</t>
+          <t>61,57; 89,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,05; 84,46</t>
+          <t>28,88; 85,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,1; 74,53</t>
+          <t>37,77; 75,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,57; 76,43</t>
+          <t>31,59; 76,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,21; 77,0</t>
+          <t>45,87; 75,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,16; 64,29</t>
+          <t>27,83; 65,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,39; 65,73</t>
+          <t>43,88; 66,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,76; 72,44</t>
+          <t>47,95; 74,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,17; 79,29</t>
+          <t>59,42; 80,79</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,3; 60,67</t>
+          <t>15,09; 62,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,41; 65,46</t>
+          <t>31,98; 64,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,46; 77,94</t>
+          <t>41,66; 76,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,34; 72,43</t>
+          <t>48,09; 73,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,95; 89,77</t>
+          <t>27,67; 90,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,85; 77,31</t>
+          <t>40,74; 77,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,24; 91,12</t>
+          <t>50,67; 91,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,76; 67,22</t>
+          <t>40,47; 68,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,42; 63,08</t>
+          <t>26,97; 63,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42,15; 66,31</t>
+          <t>42,09; 66,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53,57; 78,96</t>
+          <t>54,16; 79,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,71; 67,49</t>
+          <t>48,33; 68,68</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,39</t>
+          <t>0,0; 71,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,37; 92,06</t>
+          <t>41,84; 92,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,46; 84,26</t>
+          <t>36,58; 84,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,68; 67,62</t>
+          <t>34,57; 67,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,26; 90,9</t>
+          <t>33,59; 90,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,96; 79,19</t>
+          <t>49,54; 79,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,02; 84,37</t>
+          <t>48,01; 83,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,16; 74,54</t>
+          <t>51,24; 74,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,5; 72,85</t>
+          <t>27,86; 75,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51,69; 77,4</t>
+          <t>52,05; 79,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,65; 78,96</t>
+          <t>51,52; 80,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,19; 67,88</t>
+          <t>47,5; 68,08</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,39; 100,0</t>
+          <t>18,87; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,37; 66,49</t>
+          <t>18,46; 67,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 64,33</t>
+          <t>8,28; 64,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,7; 61,04</t>
+          <t>22,12; 61,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,64; 82,53</t>
+          <t>20,37; 81,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,09; 57,21</t>
+          <t>22,09; 60,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,79; 69,9</t>
+          <t>33,43; 70,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,19; 61,52</t>
+          <t>37,12; 61,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33,21; 81,54</t>
+          <t>34,42; 82,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,45; 54,59</t>
+          <t>23,61; 54,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,01; 60,76</t>
+          <t>31,86; 63,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,57; 56,7</t>
+          <t>36,24; 56,33</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,13; 100,0</t>
+          <t>17,85; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,96; 81,39</t>
+          <t>42,48; 81,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,95; 56,88</t>
+          <t>11,19; 58,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,7; 52,07</t>
+          <t>18,83; 51,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>48,21; 85,46</t>
+          <t>48,71; 89,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,28; 65,4</t>
+          <t>38,71; 67,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,19; 81,36</t>
+          <t>48,23; 81,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,1; 47,13</t>
+          <t>28,35; 48,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,81; 84,97</t>
+          <t>50,26; 84,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43,38; 65,95</t>
+          <t>43,33; 65,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,38; 70,29</t>
+          <t>40,8; 70,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,5; 45,14</t>
+          <t>28,85; 44,43</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>37,74; 55,95</t>
+          <t>37,08; 55,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,57; 64,01</t>
+          <t>51,59; 64,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53,96; 67,83</t>
+          <t>53,55; 67,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,95; 66,32</t>
+          <t>52,38; 66,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,77; 75,29</t>
+          <t>54,18; 73,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,35; 62,2</t>
+          <t>48,52; 60,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,57; 71,94</t>
+          <t>57,41; 71,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,81; 56,62</t>
+          <t>45,89; 57,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46,8; 61,38</t>
+          <t>47,78; 61,13</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52,96; 61,54</t>
+          <t>52,23; 61,31</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58,11; 68,37</t>
+          <t>57,67; 67,53</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,05; 60,15</t>
+          <t>50,82; 60,1</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>30037</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12175; 24310</t>
+          <t>11911; 24151</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30598; 45690</t>
+          <t>30423; 45014</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24363; 36476</t>
+          <t>23765; 36242</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8123; 19137</t>
+          <t>9366; 20697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1754; 7723</t>
+          <t>1806; 7687</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11548; 22315</t>
+          <t>11682; 21719</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10363; 17323</t>
+          <t>11293; 17320</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3248; 16817</t>
+          <t>4686; 18669</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16161; 29396</t>
+          <t>16751; 29450</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45613; 63358</t>
+          <t>45752; 63885</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38211; 52754</t>
+          <t>38749; 52896</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16365; 34741</t>
+          <t>18774; 38346</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>26260</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10394; 22887</t>
+          <t>10251; 22254</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43084; 60824</t>
+          <t>41363; 60241</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26006; 39139</t>
+          <t>26572; 39858</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7332; 21868</t>
+          <t>11129; 26459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10190; 17570</t>
+          <t>10310; 17584</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14652; 27133</t>
+          <t>14543; 27024</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8440; 18007</t>
+          <t>8848; 18389</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3221; 10810</t>
+          <t>3597; 11106</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22830; 37417</t>
+          <t>22996; 37622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59931; 83654</t>
+          <t>61426; 83118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38766; 54858</t>
+          <t>38960; 55101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13449; 29035</t>
+          <t>16519; 34754</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45507</t>
+          <t>48912</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1812; 9296</t>
+          <t>1950; 9400</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20872; 36714</t>
+          <t>20441; 35962</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16424; 28359</t>
+          <t>16473; 28607</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21192; 33226</t>
+          <t>23734; 34380</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3763; 11331</t>
+          <t>3875; 11426</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11490; 21903</t>
+          <t>11099; 22263</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8660; 19143</t>
+          <t>7914; 19038</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12954; 21586</t>
+          <t>13975; 23081</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7700; 18225</t>
+          <t>7888; 18698</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35926; 54423</t>
+          <t>36329; 54997</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28477; 44118</t>
+          <t>29202; 45561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37832; 51566</t>
+          <t>41008; 55758</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>34686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45805</t>
+          <t>52595</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2794; 11855</t>
+          <t>2948; 12209</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11358; 23672</t>
+          <t>11565; 23248</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11664; 22473</t>
+          <t>12011; 22197</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21972; 36722</t>
+          <t>26898; 41278</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2218; 8676</t>
+          <t>2674; 8779</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14990; 27046</t>
+          <t>14255; 27124</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12546; 22310</t>
+          <t>12406; 22289</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11390; 19752</t>
+          <t>13199; 22199</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7132; 18421</t>
+          <t>7877; 18576</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29991; 47176</t>
+          <t>29947; 47489</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28560; 42099</t>
+          <t>28879; 42216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37408; 54047</t>
+          <t>42797; 60818</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22401</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>40366</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6503</t>
+          <t>0; 6683</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4441; 11895</t>
+          <t>5407; 11908</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4261; 11787</t>
+          <t>5117; 11835</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9167; 19563</t>
+          <t>10889; 21210</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3283; 8973</t>
+          <t>3316; 8939</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20443; 33066</t>
+          <t>20687; 33096</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15489; 25614</t>
+          <t>14574; 25439</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17750; 26380</t>
+          <t>19625; 28682</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5484; 14018</t>
+          <t>5361; 14534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28265; 42319</t>
+          <t>28460; 43279</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22018; 35017</t>
+          <t>22848; 35534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30354; 43664</t>
+          <t>33158; 47523</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>25228</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>809; 4653</t>
+          <t>878; 4653</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3178; 11501</t>
+          <t>3193; 11599</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>887; 7033</t>
+          <t>905; 7037</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3534; 9941</t>
+          <t>4011; 11170</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1881; 7521</t>
+          <t>1856; 7462</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4835; 14492</t>
+          <t>5595; 15334</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9314; 20481</t>
+          <t>9795; 20739</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12250; 20266</t>
+          <t>13442; 22309</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4572; 11226</t>
+          <t>4739; 11324</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10847; 23270</t>
+          <t>10063; 23141</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12477; 24445</t>
+          <t>12818; 25439</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17513; 27914</t>
+          <t>19694; 30611</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27218</t>
+          <t>29028</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1075; 5933</t>
+          <t>1059; 5933</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8583; 17932</t>
+          <t>9359; 17934</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1663; 8637</t>
+          <t>1699; 8844</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4086; 10797</t>
+          <t>4334; 11801</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10895; 19313</t>
+          <t>11009; 20255</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20203; 35443</t>
+          <t>20977; 36459</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18536; 32649</t>
+          <t>19353; 32625</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14877; 24953</t>
+          <t>16060; 27205</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14212; 24245</t>
+          <t>14341; 24102</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33065; 50266</t>
+          <t>33025; 49703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22336; 38882</t>
+          <t>22567; 39150</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20998; 33262</t>
+          <t>22984; 35398</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>132316</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>108262</t>
+          <t>120111</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>226020</t>
+          <t>252427</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>46445; 68865</t>
+          <t>45632; 68392</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>149176; 181649</t>
+          <t>146400; 181897</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107727; 135418</t>
+          <t>106898; 135360</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>101920; 132688</t>
+          <t>115781; 146970</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>51379; 70627</t>
+          <t>50824; 69211</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>125526; 158211</t>
+          <t>123411; 153519</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>109543; 136873</t>
+          <t>109229; 136949</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>95708; 120943</t>
+          <t>106555; 133540</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>101500; 133121</t>
+          <t>103625; 132591</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>284961; 331171</t>
+          <t>281031; 329930</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>226554; 266569</t>
+          <t>224871; 263315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>207018; 248835</t>
+          <t>230300; 272390</t>
         </is>
       </c>
     </row>
